--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487897_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487897_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6409</v>
+        <v>2.6307</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4775</v>
+        <v>2.5846</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1635</v>
+        <v>0.046</v>
       </c>
       <c r="G2" t="n">
         <v>2.9616</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.715</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0439</v>
+        <v>-0.9367</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3289</v>
+        <v>0.2114</v>
       </c>
       <c r="V2" t="n">
         <v>-0.23</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.623</v>
+        <v>1.9889</v>
       </c>
       <c r="E3" t="n">
-        <v>2.19</v>
+        <v>1.7613</v>
       </c>
       <c r="F3" t="n">
-        <v>0.433</v>
+        <v>0.2275</v>
       </c>
       <c r="G3" t="n">
         <v>0.3032</v>
@@ -688,13 +688,13 @@
         <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9036</v>
+        <v>0.2694</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0619</v>
+        <v>-0.3667</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8416</v>
+        <v>0.6361</v>
       </c>
       <c r="V3" t="n">
         <v>0.5838</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.29</v>
+        <v>1.7685</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8204</v>
+        <v>1.0347</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4695</v>
+        <v>0.7338</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0132</v>
@@ -766,13 +766,13 @@
         <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9049</v>
+        <v>-0.4264</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6524</v>
+        <v>-0.4381</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2525</v>
+        <v>0.0118</v>
       </c>
       <c r="V4" t="n">
         <v>1.1675</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>A. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0109</v>
+        <v>0.6649</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4289</v>
+        <v>0.3145</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.418</v>
+        <v>0.3504</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1458</v>
+        <v>0.8188</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4136</v>
+        <v>-1.1684</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2678</v>
+        <v>1.9872</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4357</v>
+        <v>1.7047</v>
       </c>
       <c r="K5" t="n">
-        <v>2.279</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1568</v>
+        <v>2.3423</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2899</v>
+        <v>-0.8859</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1346</v>
+        <v>-0.5308</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4245</v>
+        <v>-0.3551</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -844,28 +844,28 @@
         <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0326</v>
+        <v>-0.1538</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1338</v>
+        <v>-0.3495</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1664</v>
+        <v>0.1957</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. OROZCO DOMINGUEZ</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4403</v>
+        <v>0.4355</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2074</v>
+        <v>2.0003</v>
       </c>
       <c r="F6" t="n">
-        <v>0.233</v>
+        <v>-1.5648</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8188</v>
+        <v>2.1458</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1684</v>
+        <v>2.4136</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9872</v>
+        <v>-0.2678</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7047</v>
+        <v>2.4357</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6375999999999999</v>
+        <v>2.279</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3423</v>
+        <v>0.1568</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8859</v>
+        <v>-0.2899</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5308</v>
+        <v>0.1346</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3551</v>
+        <v>-0.4245</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,22 +922,22 @@
         <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3784</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4567</v>
+        <v>-0.5624</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0196</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2841</v>
+        <v>-1.1769</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6182</v>
+        <v>-1.5111</v>
       </c>
       <c r="F7" t="n">
         <v>0.3342</v>
@@ -1000,10 +1000,10 @@
         <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7144</v>
+        <v>-0.6072</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3262</v>
+        <v>-0.2191</v>
       </c>
       <c r="U7" t="n">
         <v>-0.3882</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4586</v>
+        <v>-2.1221</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9564</v>
+        <v>-3.385</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4978</v>
+        <v>1.2629</v>
       </c>
       <c r="G8" t="n">
         <v>1.332</v>
@@ -1078,13 +1078,13 @@
         <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1854</v>
+        <v>0.5219</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3229</v>
+        <v>-0.1057</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8625</v>
+        <v>0.6277</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BLACK</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7235</v>
+        <v>-2.1633</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0006</v>
+        <v>-1.2803</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.723</v>
+        <v>-0.8831</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1897</v>
+        <v>-2.4809</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.695</v>
+        <v>-1.4391</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5054</v>
+        <v>-1.0418</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8262</v>
+        <v>-0.4274</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6826</v>
+        <v>-0.949</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3635</v>
+        <v>-2.0535</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0124</v>
+        <v>-0.4901</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.351</v>
+        <v>-1.5634</v>
       </c>
       <c r="P9" t="n">
         <v>1.2487</v>
@@ -1156,28 +1156,28 @@
         <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3851</v>
+        <v>-0.9312</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1744</v>
+        <v>-0.8529</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2107</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>J. BLACK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8665</v>
+        <v>-2.3037</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6017</v>
+        <v>-1.7863</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2647</v>
+        <v>-0.5174</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4809</v>
+        <v>-1.1897</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4391</v>
+        <v>-1.695</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0418</v>
+        <v>0.5054</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4274</v>
+        <v>-0.8262</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.949</v>
+        <v>-1.6826</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0535</v>
+        <v>-0.3635</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4901</v>
+        <v>-0.0124</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5634</v>
+        <v>-0.351</v>
       </c>
       <c r="P10" t="n">
         <v>1.2487</v>
@@ -1234,22 +1234,22 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6343</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1744</v>
+        <v>-0.9601</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4599</v>
+        <v>-0.0052</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1553</v>
+        <v>-2.96</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9719</v>
+        <v>-0.8647</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1834</v>
+        <v>-2.0953</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7362</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3327</v>
+        <v>-0.1375</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7177</v>
+        <v>-0.6105</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3849</v>
+        <v>0.473</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3351</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3414</v>
+        <v>-3.5866</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8999</v>
+        <v>-1.7928</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4415</v>
+        <v>-1.7938</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7923</v>
@@ -1390,13 +1390,13 @@
         <v>1.2487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2192</v>
+        <v>-0.4643</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0439</v>
+        <v>-0.9367</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8247</v>
+        <v>0.4724</v>
       </c>
       <c r="V12" t="n">
         <v>0.5838</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.8243</v>
+        <v>-6.8241</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.924499999999999</v>
+        <v>-2.9248</v>
       </c>
       <c r="F13" t="n">
         <v>-3.8996</v>
@@ -1435,7 +1435,7 @@
         <v>1.530699999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4693999999999996</v>
+        <v>0.4694</v>
       </c>
       <c r="I13" t="n">
         <v>1.0613</v>
@@ -1450,7 +1450,7 @@
         <v>6.5516</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.492100000000001</v>
+        <v>-7.4921</v>
       </c>
       <c r="N13" t="n">
         <v>-2.0018</v>
@@ -1471,7 +1471,7 @@
         <v>-4.1624</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.3386</v>
+        <v>-6.3384</v>
       </c>
       <c r="U13" t="n">
         <v>2.176</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>J. JIMÉNEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5537</v>
+        <v>3.4862</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1231</v>
+        <v>4.7987</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4306</v>
+        <v>-1.3125</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2659</v>
+        <v>2.7774</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9444</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6784</v>
+        <v>3.3424</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4132</v>
+        <v>4.3084</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0997</v>
+        <v>0.2598</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3135</v>
+        <v>4.0486</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1473</v>
+        <v>-1.531</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1553</v>
+        <v>-0.8248</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9919</v>
+        <v>-0.7062</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.7055</v>
+        <v>1.4568</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.3705</v>
+        <v>-0.2081</v>
       </c>
       <c r="R14" t="n">
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4283</v>
+        <v>0.1895</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5153</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9129</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>2.565</v>
+        <v>-0.9376</v>
       </c>
       <c r="W14" t="n">
-        <v>2.565</v>
+        <v>1.3975</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1545</v>
+        <v>3.2942</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5844</v>
+        <v>1.4801</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4299</v>
+        <v>1.8141</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7774</v>
+        <v>2.2659</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5649999999999999</v>
+        <v>2.9444</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3424</v>
+        <v>-0.6784</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3084</v>
+        <v>3.4132</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2598</v>
+        <v>3.0997</v>
       </c>
       <c r="L15" t="n">
-        <v>4.0486</v>
+        <v>0.3135</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.531</v>
+        <v>-1.1473</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8248</v>
+        <v>-0.1553</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7062</v>
+        <v>-0.9919</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4568</v>
+        <v>-2.7055</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2081</v>
+        <v>-4.3705</v>
       </c>
       <c r="R15" t="n">
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1422</v>
+        <v>1.1688</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9134</v>
+        <v>-0.1276</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7712</v>
+        <v>1.2964</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9376</v>
+        <v>2.565</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3975</v>
+        <v>2.565</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.3351</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6638</v>
+        <v>2.9478</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5971</v>
+        <v>3.5783</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0667</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2858</v>
+        <v>0.4826</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4818</v>
+        <v>1.6632</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1959</v>
+        <v>-1.1805</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2815</v>
+        <v>3.1689</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4901</v>
+        <v>2.3941</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7715</v>
+        <v>0.7748</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5673</v>
+        <v>-2.6863</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0083</v>
+        <v>-0.731</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5756</v>
+        <v>-1.9553</v>
       </c>
       <c r="P16" t="n">
         <v>1.2487</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1293</v>
+        <v>0.0489</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7111</v>
+        <v>-0.55</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4182</v>
+        <v>0.599</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="W16" t="n">
         <v>1.1675</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4898</v>
+        <v>2.5875</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1497</v>
+        <v>1.1685</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6599</v>
+        <v>1.419</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4826</v>
+        <v>0.2858</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6632</v>
+        <v>0.4818</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1805</v>
+        <v>-0.1959</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1689</v>
+        <v>-0.2815</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3941</v>
+        <v>0.4901</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7748</v>
+        <v>-0.7715</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6863</v>
+        <v>0.5673</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.731</v>
+        <v>-0.0083</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.9553</v>
+        <v>0.5756</v>
       </c>
       <c r="P17" t="n">
         <v>1.2487</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4091</v>
+        <v>1.053</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9786</v>
+        <v>0.2824</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5696</v>
+        <v>0.7705</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>1.1675</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3003</v>
+        <v>2.3869</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1202</v>
+        <v>0.4417</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1801</v>
+        <v>1.9452</v>
       </c>
       <c r="G18" t="n">
         <v>0.1925</v>
@@ -1858,13 +1858,13 @@
         <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4835</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8482</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3316</v>
+        <v>1.0967</v>
       </c>
       <c r="V18" t="n">
         <v>0.5838</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3241</v>
+        <v>1.694</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7356</v>
+        <v>1.1642</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5885</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.6736</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.182</v>
+        <v>0.1879</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6524</v>
+        <v>-0.2238</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4704</v>
+        <v>0.4117</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4641</v>
+        <v>-0.7665</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2983</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1659</v>
+        <v>-0.254</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2749</v>
@@ -2014,13 +2014,13 @@
         <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6433</v>
+        <v>0.3409</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1924</v>
+        <v>-0.0219</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4508</v>
+        <v>0.3628</v>
       </c>
       <c r="V20" t="n">
         <v>0.5838</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4454</v>
+        <v>-1.5423</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6245</v>
+        <v>-1.8388</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1791</v>
+        <v>0.2965</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0729</v>
@@ -2092,13 +2092,13 @@
         <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3112</v>
+        <v>0.2143</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1338</v>
+        <v>-0.3481</v>
       </c>
       <c r="U21" t="n">
-        <v>0.445</v>
+        <v>0.5624</v>
       </c>
       <c r="V21" t="n">
         <v>1.3975</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2556</v>
+        <v>-2.1191</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6505</v>
+        <v>-1.5434</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6051</v>
+        <v>-0.5757</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0795</v>
@@ -2170,13 +2170,13 @@
         <v>0.2081</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3843</v>
+        <v>-0.2478</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.261</v>
+        <v>-0.1538</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1233</v>
+        <v>-0.0939</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5432</v>
+        <v>-2.533</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3603</v>
+        <v>-3.4674</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.9345</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5158</v>
@@ -2248,13 +2248,13 @@
         <v>0.4162</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5969</v>
+        <v>0.6072</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.4115</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.1957</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9536</v>
+        <v>-2.6116</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.477</v>
+        <v>-1.3698</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4767</v>
+        <v>-1.2418</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2655</v>
@@ -2326,13 +2326,13 @@
         <v>0.8325</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3125</v>
+        <v>0.0295</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3262</v>
+        <v>-0.2191</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0137</v>
+        <v>0.2486</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1675</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.824299999999999</v>
+        <v>6.8241</v>
       </c>
       <c r="E25" t="n">
-        <v>3.899499999999998</v>
+        <v>3.899500000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>2.9245</v>
+        <v>2.924500000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-1.5308</v>
@@ -2404,13 +2404,13 @@
         <v>11.4464</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1624</v>
+        <v>4.162299999999999</v>
       </c>
       <c r="T25" t="n">
         <v>-2.1762</v>
       </c>
       <c r="U25" t="n">
-        <v>6.338399999999999</v>
+        <v>6.338500000000001</v>
       </c>
       <c r="V25" t="n">
         <v>4.192500000000001</v>
